--- a/data/processed/forecasts/AC_PANRITITIS_FORECAST.xlsx
+++ b/data/processed/forecasts/AC_PANRITITIS_FORECAST.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythoncoding\Final_year_project\data\processed\forecasts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1170" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -58,11 +63,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +131,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -172,7 +185,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -204,9 +217,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -238,6 +252,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -413,11 +428,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,7 +486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>45474</v>
       </c>
@@ -469,7 +497,7 @@
         <v>-1.144751664578697</v>
       </c>
       <c r="D2">
-        <v>4.359714457039461</v>
+        <v>4.3597144570394608</v>
       </c>
       <c r="E2">
         <v>1.50397146</v>
@@ -499,7 +527,7 @@
         <v>1.50397146</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>45505</v>
       </c>
@@ -507,10 +535,10 @@
         <v>1.859478129123288</v>
       </c>
       <c r="C3">
-        <v>-1.025900849938645</v>
+        <v>-1.0259008499386451</v>
       </c>
       <c r="D3">
-        <v>4.507534800517996</v>
+        <v>4.5075348005179956</v>
       </c>
       <c r="E3">
         <v>1.859478129123288</v>
@@ -540,24 +568,24 @@
         <v>1.859478129123288</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>45536</v>
       </c>
       <c r="B4">
-        <v>2.214984798537923</v>
+        <v>2.2149847985379232</v>
       </c>
       <c r="C4">
-        <v>-0.5254080021086346</v>
+        <v>-0.52540800210863459</v>
       </c>
       <c r="D4">
-        <v>5.078666871207905</v>
+        <v>5.0786668712079051</v>
       </c>
       <c r="E4">
-        <v>2.214984798537923</v>
+        <v>2.2149847985379232</v>
       </c>
       <c r="F4">
-        <v>2.214984798537923</v>
+        <v>2.2149847985379232</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -578,27 +606,27 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2.214984798537923</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>2.2149847985379232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>45566</v>
       </c>
       <c r="B5">
-        <v>2.55902351114742</v>
+        <v>2.5590235111474202</v>
       </c>
       <c r="C5">
         <v>-0.1171710303404561</v>
       </c>
       <c r="D5">
-        <v>5.444547174811148</v>
+        <v>5.4445471748111478</v>
       </c>
       <c r="E5">
-        <v>2.55902351114742</v>
+        <v>2.5590235111474202</v>
       </c>
       <c r="F5">
-        <v>2.55902351114742</v>
+        <v>2.5590235111474202</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -619,27 +647,27 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2.55902351114742</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>2.5590235111474202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>45597</v>
       </c>
       <c r="B6">
-        <v>2.914530180714629</v>
+        <v>2.9145301807146291</v>
       </c>
       <c r="C6">
-        <v>0.05468604575872461</v>
+        <v>5.4686045758724607E-2</v>
       </c>
       <c r="D6">
-        <v>5.770973810510363</v>
+        <v>5.7709738105103634</v>
       </c>
       <c r="E6">
-        <v>2.914530180714629</v>
+        <v>2.9145301807146291</v>
       </c>
       <c r="F6">
-        <v>2.914530180714629</v>
+        <v>2.9145301807146291</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -660,27 +688,27 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2.914530180714629</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>2.9145301807146291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>45627</v>
       </c>
       <c r="B7">
-        <v>3.258568893076782</v>
+        <v>3.2585688930767822</v>
       </c>
       <c r="C7">
-        <v>0.6411122272751127</v>
+        <v>0.64111222727511274</v>
       </c>
       <c r="D7">
-        <v>6.018281429007668</v>
+        <v>6.0182814290076676</v>
       </c>
       <c r="E7">
-        <v>3.258568893076782</v>
+        <v>3.2585688930767822</v>
       </c>
       <c r="F7">
-        <v>3.258568893076782</v>
+        <v>3.2585688930767822</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -701,27 +729,27 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>3.258568893076782</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>3.2585688930767822</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>45658</v>
       </c>
       <c r="B8">
-        <v>3.614075562783042</v>
+        <v>3.6140755627830421</v>
       </c>
       <c r="C8">
-        <v>0.9067928651616312</v>
+        <v>0.90679286516163116</v>
       </c>
       <c r="D8">
-        <v>6.435505714080547</v>
+        <v>6.4355057140805467</v>
       </c>
       <c r="E8">
-        <v>3.614075562783042</v>
+        <v>3.6140755627830421</v>
       </c>
       <c r="F8">
-        <v>3.614075562783042</v>
+        <v>3.6140755627830421</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -742,27 +770,27 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>3.614075562783042</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>3.6140755627830421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>45689</v>
       </c>
       <c r="B9">
-        <v>3.969582232519042</v>
+        <v>3.9695822325190422</v>
       </c>
       <c r="C9">
         <v>1.040013418675984</v>
       </c>
       <c r="D9">
-        <v>6.793226245484884</v>
+        <v>6.7932262454848837</v>
       </c>
       <c r="E9">
-        <v>3.969582232519042</v>
+        <v>3.9695822325190422</v>
       </c>
       <c r="F9">
-        <v>3.969582232519042</v>
+        <v>3.9695822325190422</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -783,27 +811,27 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>3.969582232519042</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>3.9695822325190422</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>45717</v>
       </c>
       <c r="B10">
-        <v>4.290685031063335</v>
+        <v>4.2906850310633349</v>
       </c>
       <c r="C10">
         <v>1.508387744396797</v>
       </c>
       <c r="D10">
-        <v>7.047841222595793</v>
+        <v>7.0478412225957934</v>
       </c>
       <c r="E10">
-        <v>4.290685031063335</v>
+        <v>4.2906850310633349</v>
       </c>
       <c r="F10">
-        <v>4.290685031063335</v>
+        <v>4.2906850310633349</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -824,27 +852,27 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>4.290685031063335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>4.2906850310633349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>45748</v>
       </c>
       <c r="B11">
-        <v>4.64619170077629</v>
+        <v>4.6461917007762903</v>
       </c>
       <c r="C11">
         <v>1.924016776183433</v>
       </c>
       <c r="D11">
-        <v>7.392127835556282</v>
+        <v>7.3921278355562823</v>
       </c>
       <c r="E11">
-        <v>4.64619170077629</v>
+        <v>4.6461917007762903</v>
       </c>
       <c r="F11">
-        <v>4.64619170077629</v>
+        <v>4.6461917007762903</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -865,27 +893,27 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>4.64619170077629</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>4.6461917007762903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>45778</v>
       </c>
       <c r="B12">
-        <v>4.990230413399358</v>
+        <v>4.9902304133993578</v>
       </c>
       <c r="C12">
-        <v>2.466074866139482</v>
+        <v>2.4660748661394818</v>
       </c>
       <c r="D12">
-        <v>7.653016889079113</v>
+        <v>7.6530168890791126</v>
       </c>
       <c r="E12">
-        <v>4.990230413399358</v>
+        <v>4.9902304133993578</v>
       </c>
       <c r="F12">
-        <v>4.990230413399358</v>
+        <v>4.9902304133993578</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -906,27 +934,27 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>4.990230413399358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>4.9902304133993578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>45809</v>
       </c>
       <c r="B13">
-        <v>5.345737083109862</v>
+        <v>5.3457370831098618</v>
       </c>
       <c r="C13">
-        <v>2.658567075711362</v>
+        <v>2.6585670757113622</v>
       </c>
       <c r="D13">
-        <v>8.218478211480667</v>
+        <v>8.2184782114806669</v>
       </c>
       <c r="E13">
-        <v>5.345737083109862</v>
+        <v>5.3457370831098618</v>
       </c>
       <c r="F13">
-        <v>5.345737083109862</v>
+        <v>5.3457370831098618</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -947,27 +975,27 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>5.345737083109862</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>5.3457370831098618</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>45839</v>
       </c>
       <c r="B14">
-        <v>5.68977579573293</v>
+        <v>5.6897757957329302</v>
       </c>
       <c r="C14">
         <v>2.899360523181409</v>
       </c>
       <c r="D14">
-        <v>8.334440493235489</v>
+        <v>8.3344404932354887</v>
       </c>
       <c r="E14">
-        <v>5.68977579573293</v>
+        <v>5.6897757957329302</v>
       </c>
       <c r="F14">
-        <v>5.68977579573293</v>
+        <v>5.6897757957329302</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -988,24 +1016,24 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>5.68977579573293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>5.6897757957329302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>45870</v>
       </c>
       <c r="B15">
-        <v>6.045282465443433</v>
+        <v>6.0452824654434334</v>
       </c>
       <c r="C15">
-        <v>3.190307396092264</v>
+        <v>3.1903073960922641</v>
       </c>
       <c r="D15">
-        <v>8.565631181983239</v>
+        <v>8.5656311819832389</v>
       </c>
       <c r="E15">
-        <v>6.045282460796846</v>
+        <v>6.0452824607968463</v>
       </c>
       <c r="F15">
         <v>6.045282470904243</v>
@@ -1029,27 +1057,27 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>6.045282465443433</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>6.0452824654434334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>45901</v>
       </c>
       <c r="B16">
-        <v>6.400789135153937</v>
+        <v>6.4007891351539374</v>
       </c>
       <c r="C16">
-        <v>3.80539245923936</v>
+        <v>3.8053924592393602</v>
       </c>
       <c r="D16">
-        <v>9.282433101588328</v>
+        <v>9.2824331015883281</v>
       </c>
       <c r="E16">
-        <v>6.400789119599811</v>
+        <v>6.4007891195998106</v>
       </c>
       <c r="F16">
-        <v>6.400789153047235</v>
+        <v>6.4007891530472349</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1070,27 +1098,27 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>6.400789135153937</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>6.4007891351539374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>45931</v>
       </c>
       <c r="B17">
-        <v>6.744827847777007</v>
+        <v>6.7448278477770067</v>
       </c>
       <c r="C17">
-        <v>4.012431489355521</v>
+        <v>4.0124314893555209</v>
       </c>
       <c r="D17">
-        <v>9.385207279930189</v>
+        <v>9.3852072799301887</v>
       </c>
       <c r="E17">
         <v>6.744827818787388</v>
       </c>
       <c r="F17">
-        <v>6.744827879613725</v>
+        <v>6.7448278796137249</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1111,10 +1139,10 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>6.744827847777007</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>6.7448278477770067</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>45962</v>
       </c>
@@ -1122,16 +1150,16 @@
         <v>7.100334517487509</v>
       </c>
       <c r="C18">
-        <v>4.574582511245116</v>
+        <v>4.5745825112451159</v>
       </c>
       <c r="D18">
         <v>10.10930352904213</v>
       </c>
       <c r="E18">
-        <v>7.100334468759056</v>
+        <v>7.1003344687590557</v>
       </c>
       <c r="F18">
-        <v>7.100334567413181</v>
+        <v>7.1003345674131806</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1155,24 +1183,24 @@
         <v>7.100334517487509</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>45992</v>
       </c>
       <c r="B19">
-        <v>7.444373230110577</v>
+        <v>7.4443732301105774</v>
       </c>
       <c r="C19">
-        <v>4.793308881948806</v>
+        <v>4.7933088819488061</v>
       </c>
       <c r="D19">
-        <v>10.28820235913611</v>
+        <v>10.288202359136109</v>
       </c>
       <c r="E19">
-        <v>7.444373162496722</v>
+        <v>7.4443731624967224</v>
       </c>
       <c r="F19">
-        <v>7.444373303301136</v>
+        <v>7.4443733033011359</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1193,27 +1221,27 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>7.444373230110577</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>7.4443732301105774</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46023</v>
       </c>
       <c r="B20">
-        <v>7.799879899821081</v>
+        <v>7.7998798998210814</v>
       </c>
       <c r="C20">
-        <v>4.932581440644728</v>
+        <v>4.9325814406447277</v>
       </c>
       <c r="D20">
         <v>10.62876890711027</v>
       </c>
       <c r="E20">
-        <v>7.799879806258526</v>
+        <v>7.7998798062585264</v>
       </c>
       <c r="F20">
-        <v>7.799879997219455</v>
+        <v>7.7998799972194552</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1234,27 +1262,27 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>7.799879899821081</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>7.7998798998210814</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46054</v>
       </c>
       <c r="B21">
-        <v>8.155386569531585</v>
+        <v>8.1553865695315846</v>
       </c>
       <c r="C21">
-        <v>5.594555875775414</v>
+        <v>5.5945558757754137</v>
       </c>
       <c r="D21">
-        <v>10.98094223762132</v>
+        <v>10.980942237621321</v>
       </c>
       <c r="E21">
-        <v>8.155386453417739</v>
+        <v>8.1553864534177389</v>
       </c>
       <c r="F21">
-        <v>8.155386697024552</v>
+        <v>8.1553866970245519</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1275,27 +1303,27 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>8.155386569531585</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>8.1553865695315846</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46082</v>
       </c>
       <c r="B22">
-        <v>8.476489367979781</v>
+        <v>8.4764893679797808</v>
       </c>
       <c r="C22">
-        <v>5.683341200934697</v>
+        <v>5.6833412009346969</v>
       </c>
       <c r="D22">
         <v>11.31105490869613</v>
       </c>
       <c r="E22">
-        <v>8.476489224126086</v>
+        <v>8.4764892241260856</v>
       </c>
       <c r="F22">
-        <v>8.476489528831094</v>
+        <v>8.4764895288310935</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1316,27 +1344,27 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>8.476489367979781</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>8.4764893679797808</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46113</v>
       </c>
       <c r="B23">
-        <v>8.831996037690287</v>
+        <v>8.8319960376902866</v>
       </c>
       <c r="C23">
-        <v>6.170805654233577</v>
+        <v>6.1708056542335772</v>
       </c>
       <c r="D23">
-        <v>11.72772242488113</v>
+        <v>11.727722424881129</v>
       </c>
       <c r="E23">
-        <v>8.831995866671324</v>
+        <v>8.8319958666713241</v>
       </c>
       <c r="F23">
-        <v>8.831996230188031</v>
+        <v>8.8319962301880306</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1357,27 +1385,27 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>8.831996037690287</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>8.8319960376902866</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46143</v>
       </c>
       <c r="B24">
-        <v>9.176034750313352</v>
+        <v>9.1760347503133524</v>
       </c>
       <c r="C24">
-        <v>6.55151160411671</v>
+        <v>6.5515116041167101</v>
       </c>
       <c r="D24">
         <v>12.05941104727335</v>
       </c>
       <c r="E24">
-        <v>9.176034548356235</v>
+        <v>9.1760345483562347</v>
       </c>
       <c r="F24">
-        <v>9.176034981867147</v>
+        <v>9.1760349818671472</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1398,27 +1426,27 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>9.176034750313352</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>9.1760347503133524</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46174</v>
       </c>
       <c r="B25">
-        <v>9.531541420023858</v>
+        <v>9.5315414200238582</v>
       </c>
       <c r="C25">
-        <v>6.928974760839664</v>
+        <v>6.9289747608396643</v>
       </c>
       <c r="D25">
-        <v>12.38795551854703</v>
+        <v>12.387955518547029</v>
       </c>
       <c r="E25">
-        <v>9.53154118169202</v>
+        <v>9.5315411816920204</v>
       </c>
       <c r="F25">
-        <v>9.531541687373302</v>
+        <v>9.5315416873733021</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1439,27 +1467,27 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>9.531541420023858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>9.5315414200238582</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46204</v>
       </c>
       <c r="B26">
-        <v>9.875580132646926</v>
+        <v>9.8755801326469257</v>
       </c>
       <c r="C26">
-        <v>7.184904580627544</v>
+        <v>7.1849045806275438</v>
       </c>
       <c r="D26">
         <v>12.56101157203593</v>
       </c>
       <c r="E26">
-        <v>9.875579855922579</v>
+        <v>9.8755798559225791</v>
       </c>
       <c r="F26">
-        <v>9.875580438386557</v>
+        <v>9.8755804383865566</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1480,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>9.875580132646926</v>
+        <v>9.8755801326469257</v>
       </c>
     </row>
   </sheetData>
